--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.16152516076429</v>
+        <v>3.601247838624197</v>
       </c>
       <c r="D2" t="n">
-        <v>38.59026605542523</v>
+        <v>6.270918234006601</v>
       </c>
       <c r="E2" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.84805228201955</v>
+        <v>2.575308495828177</v>
       </c>
       <c r="D3" t="n">
-        <v>22.46716204477654</v>
+        <v>3.650913832276188</v>
       </c>
       <c r="E3" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F3" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.13974362215663</v>
+        <v>2.622708338600452</v>
       </c>
       <c r="D4" t="n">
-        <v>15.00649002368974</v>
+        <v>2.438554628849583</v>
       </c>
       <c r="E4" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F4" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.35159132377184</v>
+        <v>3.957133590112925</v>
       </c>
       <c r="D5" t="n">
-        <v>13.27768478776148</v>
+        <v>2.15762377801124</v>
       </c>
       <c r="E5" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F5" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.7666138659434</v>
+        <v>2.399574753215803</v>
       </c>
       <c r="D6" t="n">
-        <v>5.558156453071389</v>
+        <v>0.9032004236241007</v>
       </c>
       <c r="E6" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F6" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.25940669922602</v>
+        <v>3.779653588624228</v>
       </c>
       <c r="D7" t="n">
-        <v>11.31420342036672</v>
+        <v>1.838558055809592</v>
       </c>
       <c r="E7" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F7" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.991010541764454</v>
+        <v>1.136039213036724</v>
       </c>
       <c r="D8" t="n">
-        <v>5.492885524314161</v>
+        <v>0.8925938977010512</v>
       </c>
       <c r="E8" t="n">
-        <v>5.659206709116964</v>
+        <v>0.9196210902315067</v>
       </c>
       <c r="F8" t="n">
-        <v>10.70325939382619</v>
+        <v>1.739279651496755</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
